--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_nuble.xlsx
@@ -404,7 +404,7 @@
         <v>26.22601279317697</v>
       </c>
       <c r="D2">
-        <v>1.634319557987625</v>
+        <v>2.860286615341805</v>
       </c>
       <c r="E2">
         <v>21.68997082788452</v>
@@ -429,7 +429,7 @@
         <v>28.01938782285373</v>
       </c>
       <c r="D3">
-        <v>1.420045257401471</v>
+        <v>2.3584403382399</v>
       </c>
       <c r="E3">
         <v>24.88019636108622</v>
@@ -454,7 +454,7 @@
         <v>23.76626565185367</v>
       </c>
       <c r="D4">
-        <v>1.953164961636828</v>
+        <v>3.645286396181384</v>
       </c>
       <c r="E4">
         <v>18.14343707713126</v>
@@ -479,7 +479,7 @@
         <v>26.2926944971537</v>
       </c>
       <c r="D5">
-        <v>1.481637673519592</v>
+        <v>2.427173287276914</v>
       </c>
       <c r="E5">
         <v>24.59817319266445</v>
@@ -504,7 +504,7 @@
         <v>27.25556813892035</v>
       </c>
       <c r="D6">
-        <v>1.444383860414395</v>
+        <v>2.382194244604317</v>
       </c>
       <c r="E6">
         <v>24.8048182020968</v>
@@ -529,7 +529,7 @@
         <v>24.20945256715403</v>
       </c>
       <c r="D7">
-        <v>1.514938186813187</v>
+        <v>2.392353579175705</v>
       </c>
       <c r="E7">
         <v>25.17921758721923</v>
@@ -554,7 +554,7 @@
         <v>25.5410225921522</v>
       </c>
       <c r="D8">
-        <v>1.339314152245461</v>
+        <v>2.035662417298693</v>
       </c>
       <c r="E8">
         <v>28.12471634746301</v>
@@ -579,7 +579,7 @@
         <v>27.13706888032414</v>
       </c>
       <c r="D9">
-        <v>1.388637299300123</v>
+        <v>2.22836379652059</v>
       </c>
       <c r="E9">
         <v>26.08870504423762</v>
@@ -604,7 +604,7 @@
         <v>26.76327693080918</v>
       </c>
       <c r="D10">
-        <v>1.446679592825981</v>
+        <v>2.360688155032628</v>
       </c>
       <c r="E10">
         <v>25.04705299653294</v>
@@ -629,7 +629,7 @@
         <v>24.9229945091737</v>
       </c>
       <c r="D11">
-        <v>1.418503039513678</v>
+        <v>2.194240376138701</v>
       </c>
       <c r="E11">
         <v>26.73002906291729</v>
@@ -654,7 +654,7 @@
         <v>25.09493670886076</v>
       </c>
       <c r="D12">
-        <v>1.250989707046714</v>
+        <v>1.823427582227351</v>
       </c>
       <c r="E12">
         <v>30.47836792120999</v>
@@ -679,7 +679,7 @@
         <v>25.78416728902166</v>
       </c>
       <c r="D13">
-        <v>1.415059445178335</v>
+        <v>2.227953410981697</v>
       </c>
       <c r="E13">
         <v>26.29909200306312</v>
@@ -704,7 +704,7 @@
         <v>23.88905457798986</v>
       </c>
       <c r="D14">
-        <v>1.297600619195047</v>
+        <v>1.880538418395962</v>
       </c>
       <c r="E14">
         <v>30.03200269496378</v>
@@ -729,7 +729,7 @@
         <v>22.72052272052272</v>
       </c>
       <c r="D15">
-        <v>1.340900039824771</v>
+        <v>1.928407789232532</v>
       </c>
       <c r="E15">
         <v>29.70398094589997</v>
@@ -754,7 +754,7 @@
         <v>32.27953410981697</v>
       </c>
       <c r="D16">
-        <v>1.448192771084337</v>
+        <v>2.719457013574661</v>
       </c>
       <c r="E16">
         <v>21.751968503937</v>
@@ -779,7 +779,7 @@
         <v>29.32675361297145</v>
       </c>
       <c r="D17">
-        <v>1.254754533392304</v>
+        <v>1.985304408677397</v>
       </c>
       <c r="E17">
         <v>28.03060023538642</v>
@@ -804,7 +804,7 @@
         <v>26.86056458511548</v>
       </c>
       <c r="D18">
-        <v>1.468469977388829</v>
+        <v>2.424975798644724</v>
       </c>
       <c r="E18">
         <v>24.53182249966074</v>
@@ -829,7 +829,7 @@
         <v>27.71413276231263</v>
       </c>
       <c r="D19">
-        <v>1.595626548219014</v>
+        <v>2.860643185298622</v>
       </c>
       <c r="E19">
         <v>21.48945272649488</v>
@@ -854,7 +854,7 @@
         <v>33.52601156069364</v>
       </c>
       <c r="D20">
-        <v>1.738179669030733</v>
+        <v>4.165722379603399</v>
       </c>
       <c r="E20">
         <v>15.23850636736456</v>
@@ -879,7 +879,7 @@
         <v>24.33192686357243</v>
       </c>
       <c r="D21">
-        <v>1.64774044032445</v>
+        <v>2.750483558994197</v>
       </c>
       <c r="E21">
         <v>22.62582056892779</v>
@@ -904,7 +904,7 @@
         <v>25.11993859144118</v>
       </c>
       <c r="D22">
-        <v>1.536035372144436</v>
+        <v>2.501079913606911</v>
       </c>
       <c r="E22">
         <v>24.21688847562039</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.22601279317697</v>
+      </c>
+      <c r="C2">
         <v>34.961531289776</v>
-      </c>
-      <c r="C2">
-        <v>26.22601279317697</v>
       </c>
       <c r="D2">
         <v>2.860286615341805</v>
       </c>
       <c r="E2">
-        <v>21.68997082788452</v>
+        <v>16.27049592596319</v>
       </c>
       <c r="F2">
         <v>62.0395332461523</v>
       </c>
       <c r="G2">
-        <v>16.27049592596319</v>
+        <v>21.68997082788452</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.01938782285373</v>
+      </c>
+      <c r="C3">
         <v>42.40090299448907</v>
-      </c>
-      <c r="C3">
-        <v>28.01938782285373</v>
       </c>
       <c r="D3">
         <v>2.3584403382399</v>
       </c>
       <c r="E3">
-        <v>24.88019636108622</v>
+        <v>16.44134491759848</v>
       </c>
       <c r="F3">
         <v>58.67845872131532</v>
       </c>
       <c r="G3">
-        <v>16.44134491759848</v>
+        <v>24.88019636108622</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>23.76626565185367</v>
+      </c>
+      <c r="C4">
         <v>27.43268679924708</v>
-      </c>
-      <c r="C4">
-        <v>23.76626565185367</v>
       </c>
       <c r="D4">
         <v>3.645286396181384</v>
       </c>
       <c r="E4">
-        <v>18.14343707713126</v>
+        <v>15.71853856562923</v>
       </c>
       <c r="F4">
         <v>66.13802435723952</v>
       </c>
       <c r="G4">
-        <v>15.71853856562923</v>
+        <v>18.14343707713126</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.2926944971537</v>
+      </c>
+      <c r="C5">
         <v>41.20018975332068</v>
-      </c>
-      <c r="C5">
-        <v>26.2926944971537</v>
       </c>
       <c r="D5">
         <v>2.427173287276914</v>
       </c>
       <c r="E5">
+        <v>15.69779791828932</v>
+      </c>
+      <c r="F5">
+        <v>59.70402888904623</v>
+      </c>
+      <c r="G5">
         <v>24.59817319266445</v>
-      </c>
-      <c r="F5">
-        <v>59.70402888904624</v>
-      </c>
-      <c r="G5">
-        <v>15.69779791828932</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.25556813892035</v>
+      </c>
+      <c r="C6">
         <v>41.97810494526236</v>
-      </c>
-      <c r="C6">
-        <v>27.25556813892035</v>
       </c>
       <c r="D6">
         <v>2.382194244604317</v>
       </c>
       <c r="E6">
-        <v>24.8048182020968</v>
+        <v>16.10528663841178</v>
       </c>
       <c r="F6">
         <v>59.08989515949141</v>
       </c>
       <c r="G6">
-        <v>16.10528663841178</v>
+        <v>24.8048182020968</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>24.20945256715403</v>
+      </c>
+      <c r="C7">
         <v>41.79984132381276</v>
-      </c>
-      <c r="C7">
-        <v>24.20945256715403</v>
       </c>
       <c r="D7">
         <v>2.392353579175705</v>
       </c>
       <c r="E7">
-        <v>25.17921758721923</v>
+        <v>14.583191097153</v>
       </c>
       <c r="F7">
-        <v>60.23759131562778</v>
+        <v>60.23759131562777</v>
       </c>
       <c r="G7">
-        <v>14.583191097153</v>
+        <v>25.17921758721922</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>25.5410225921522</v>
+      </c>
+      <c r="C8">
         <v>49.12405866032501</v>
-      </c>
-      <c r="C8">
-        <v>25.5410225921522</v>
       </c>
       <c r="D8">
         <v>2.035662417298693</v>
       </c>
       <c r="E8">
+        <v>14.62285558682037</v>
+      </c>
+      <c r="F8">
+        <v>57.25242806571661</v>
+      </c>
+      <c r="G8">
         <v>28.12471634746301</v>
-      </c>
-      <c r="F8">
-        <v>57.25242806571662</v>
-      </c>
-      <c r="G8">
-        <v>14.62285558682037</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.13706888032414</v>
+      </c>
+      <c r="C9">
         <v>44.87597588694535</v>
-      </c>
-      <c r="C9">
-        <v>27.13706888032414</v>
       </c>
       <c r="D9">
         <v>2.22836379652059</v>
       </c>
       <c r="E9">
-        <v>26.08870504423762</v>
+        <v>15.77616913707917</v>
       </c>
       <c r="F9">
         <v>58.13512581868321</v>
       </c>
       <c r="G9">
-        <v>15.77616913707917</v>
+        <v>26.08870504423762</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.76327693080918</v>
+      </c>
+      <c r="C10">
         <v>42.36052940190987</v>
-      </c>
-      <c r="C10">
-        <v>26.76327693080918</v>
       </c>
       <c r="D10">
         <v>2.360688155032628</v>
       </c>
       <c r="E10">
-        <v>25.04705299653294</v>
+        <v>15.82466567607727</v>
       </c>
       <c r="F10">
         <v>59.12828132738979</v>
       </c>
       <c r="G10">
-        <v>15.82466567607727</v>
+        <v>25.04705299653294</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.9229945091737</v>
+      </c>
+      <c r="C11">
         <v>45.57385830989688</v>
-      </c>
-      <c r="C11">
-        <v>24.9229945091737</v>
       </c>
       <c r="D11">
         <v>2.194240376138701</v>
       </c>
       <c r="E11">
-        <v>26.73002906291729</v>
+        <v>14.61786191186867</v>
       </c>
       <c r="F11">
         <v>58.65210902521405</v>
       </c>
       <c r="G11">
-        <v>14.61786191186867</v>
+        <v>26.73002906291729</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.09493670886076</v>
+      </c>
+      <c r="C12">
         <v>54.84177215189874</v>
-      </c>
-      <c r="C12">
-        <v>25.09493670886076</v>
       </c>
       <c r="D12">
         <v>1.823427582227351</v>
       </c>
       <c r="E12">
-        <v>30.47836792120999</v>
+        <v>13.94653534998241</v>
       </c>
       <c r="F12">
         <v>55.57509672880759</v>
       </c>
       <c r="G12">
-        <v>13.94653534998241</v>
+        <v>30.47836792120999</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.78416728902166</v>
+      </c>
+      <c r="C13">
         <v>44.88424197162061</v>
-      </c>
-      <c r="C13">
-        <v>25.78416728902166</v>
       </c>
       <c r="D13">
         <v>2.227953410981697</v>
       </c>
       <c r="E13">
-        <v>26.29909200306312</v>
+        <v>15.10775626299092</v>
       </c>
       <c r="F13">
         <v>58.59315173394595</v>
       </c>
       <c r="G13">
-        <v>15.10775626299092</v>
+        <v>26.29909200306312</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>23.88905457798986</v>
+      </c>
+      <c r="C14">
         <v>53.17626006561288</v>
-      </c>
-      <c r="C14">
-        <v>23.88905457798986</v>
       </c>
       <c r="D14">
         <v>1.880538418395962</v>
       </c>
       <c r="E14">
-        <v>30.03200269496378</v>
+        <v>13.49166245578575</v>
       </c>
       <c r="F14">
         <v>56.47633484925046</v>
       </c>
       <c r="G14">
-        <v>13.49166245578575</v>
+        <v>30.03200269496379</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>22.72052272052272</v>
+      </c>
+      <c r="C15">
         <v>51.85625185625186</v>
-      </c>
-      <c r="C15">
-        <v>22.72052272052272</v>
       </c>
       <c r="D15">
         <v>1.928407789232532</v>
       </c>
       <c r="E15">
-        <v>29.70398094589997</v>
+        <v>13.01463082681184</v>
       </c>
       <c r="F15">
-        <v>57.2813882272882</v>
+        <v>57.28138822728819</v>
       </c>
       <c r="G15">
-        <v>13.01463082681184</v>
+        <v>29.70398094589996</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>32.27953410981697</v>
+      </c>
+      <c r="C16">
         <v>36.7720465890183</v>
-      </c>
-      <c r="C16">
-        <v>32.27953410981697</v>
       </c>
       <c r="D16">
         <v>2.719457013574661</v>
       </c>
       <c r="E16">
-        <v>21.751968503937</v>
+        <v>19.09448818897638</v>
       </c>
       <c r="F16">
         <v>59.15354330708661</v>
       </c>
       <c r="G16">
-        <v>19.09448818897638</v>
+        <v>21.75196850393701</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.32675361297145</v>
+      </c>
+      <c r="C17">
         <v>50.37010927035601</v>
-      </c>
-      <c r="C17">
-        <v>29.32675361297145</v>
       </c>
       <c r="D17">
         <v>1.985304408677397</v>
       </c>
       <c r="E17">
-        <v>28.03060023538642</v>
+        <v>16.32012553942723</v>
       </c>
       <c r="F17">
         <v>55.64927422518635</v>
       </c>
       <c r="G17">
-        <v>16.32012553942723</v>
+        <v>28.03060023538642</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.86056458511548</v>
+      </c>
+      <c r="C18">
         <v>41.2375249500998</v>
-      </c>
-      <c r="C18">
-        <v>26.86056458511548</v>
       </c>
       <c r="D18">
         <v>2.424975798644724</v>
       </c>
       <c r="E18">
+        <v>15.97910164201384</v>
+      </c>
+      <c r="F18">
+        <v>59.48907585832542</v>
+      </c>
+      <c r="G18">
         <v>24.53182249966074</v>
-      </c>
-      <c r="F18">
-        <v>59.48907585832541</v>
-      </c>
-      <c r="G18">
-        <v>15.97910164201384</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.71413276231263</v>
+      </c>
+      <c r="C19">
         <v>34.95717344753747</v>
-      </c>
-      <c r="C19">
-        <v>27.71413276231263</v>
       </c>
       <c r="D19">
         <v>2.860643185298622</v>
       </c>
       <c r="E19">
+        <v>17.03689077566064</v>
+      </c>
+      <c r="F19">
+        <v>61.47365649784447</v>
+      </c>
+      <c r="G19">
         <v>21.48945272649488</v>
-      </c>
-      <c r="F19">
-        <v>61.47365649784448</v>
-      </c>
-      <c r="G19">
-        <v>17.03689077566064</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>33.52601156069364</v>
+      </c>
+      <c r="C20">
         <v>24.00544032641958</v>
-      </c>
-      <c r="C20">
-        <v>33.52601156069364</v>
       </c>
       <c r="D20">
         <v>4.165722379603399</v>
       </c>
       <c r="E20">
+        <v>21.282106626376</v>
+      </c>
+      <c r="F20">
+        <v>63.47938700625945</v>
+      </c>
+      <c r="G20">
         <v>15.23850636736456</v>
-      </c>
-      <c r="F20">
-        <v>63.47938700625944</v>
-      </c>
-      <c r="G20">
-        <v>21.282106626376</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>24.33192686357243</v>
+      </c>
+      <c r="C21">
         <v>36.35724331926863</v>
-      </c>
-      <c r="C21">
-        <v>24.33192686357243</v>
       </c>
       <c r="D21">
         <v>2.750483558994197</v>
       </c>
       <c r="E21">
-        <v>22.62582056892779</v>
+        <v>15.14223194748359</v>
       </c>
       <c r="F21">
         <v>62.23194748358863</v>
       </c>
       <c r="G21">
-        <v>15.14223194748359</v>
+        <v>22.62582056892779</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.11993859144118</v>
+      </c>
+      <c r="C22">
         <v>39.98272884283247</v>
-      </c>
-      <c r="C22">
-        <v>25.11993859144118</v>
       </c>
       <c r="D22">
         <v>2.501079913606911</v>
       </c>
       <c r="E22">
-        <v>24.21688847562039</v>
+        <v>15.21473818794677</v>
       </c>
       <c r="F22">
         <v>60.56837333643285</v>
       </c>
       <c r="G22">
-        <v>15.21473818794677</v>
+        <v>24.21688847562039</v>
       </c>
     </row>
   </sheetData>
